--- a/public/客户报单排序模板批量导入模板.xlsx
+++ b/public/客户报单排序模板批量导入模板.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户模板配置批量导入" sheetId="1" r:id="R5b86c7c99b264a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R1ca0d37fec884d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户模板配置批量导入" sheetId="1" r:id="Raa3ed006cc6044cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R28997aa1090e4022"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,9 +466,9 @@
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -483,7 +483,7 @@
       <x:c r="F1" s="4"/>
       <x:c r="G1" s="4"/>
       <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
+      <x:c r="I1"/>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="8" t="str">
@@ -496,7 +496,11 @@
       <x:c r="F2" s="8"/>
       <x:c r="G2" s="8"/>
       <x:c r="H2" s="8"/>
-      <x:c r="I2" s="8"/>
+      <x:c r="I2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="17" t="str">
@@ -518,14 +522,12 @@
         <x:v>交易方向*</x:v>
       </x:c>
       <x:c r="G4" s="18" t="str">
-        <x:v>开平标志*</x:v>
+        <x:v>报单排序模板*</x:v>
       </x:c>
       <x:c r="H4" s="18" t="str">
-        <x:v>报单排序模板*</x:v>
-      </x:c>
-      <x:c r="I4" s="19" t="str">
         <x:v>导入方式*</x:v>
       </x:c>
+      <x:c r="I4"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="31" t="str">
@@ -544,17 +546,15 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="F5" s="28" t="str">
-        <x:v>买</x:v>
+        <x:v>买入</x:v>
       </x:c>
       <x:c r="G5" s="28" t="str">
-        <x:v>默认</x:v>
+        <x:v>test1</x:v>
       </x:c>
       <x:c r="H5" s="28" t="str">
-        <x:v>test1</x:v>
-      </x:c>
-      <x:c r="I5" s="28" t="str">
         <x:v>新增</x:v>
       </x:c>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="32" t="str">
@@ -573,17 +573,15 @@
         <x:v>聚丙烯|白银</x:v>
       </x:c>
       <x:c r="F6" s="29" t="str">
-        <x:v>卖</x:v>
+        <x:v>卖开</x:v>
       </x:c>
       <x:c r="G6" s="29" t="str">
-        <x:v>开仓</x:v>
+        <x:v>test1</x:v>
       </x:c>
       <x:c r="H6" s="29" t="str">
-        <x:v>test1</x:v>
-      </x:c>
-      <x:c r="I6" s="29" t="str">
         <x:v>新增</x:v>
       </x:c>
+      <x:c r="I6"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="33" t="str">
@@ -602,617 +600,1015 @@
         <x:v>全部</x:v>
       </x:c>
       <x:c r="F7" s="30" t="str">
-        <x:v>买</x:v>
+        <x:v>买平</x:v>
       </x:c>
       <x:c r="G7" s="30" t="str">
-        <x:v>平仓</x:v>
+        <x:v>默认模板</x:v>
       </x:c>
       <x:c r="H7" s="30" t="str">
-        <x:v>默认模板</x:v>
-      </x:c>
-      <x:c r="I7" s="30" t="str">
         <x:v>覆盖</x:v>
       </x:c>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="34"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="34"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="34"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="34"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="34"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="34"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="34"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="34"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="34"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="34"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="34"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="34"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="34"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="34"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="34"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="34"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="34"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="34"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="34"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="34"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="34"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="34"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="34"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="34"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="34"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="34"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="34"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="34"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="34"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="34"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="34"/>
+      <x:c r="G39"/>
+      <x:c r="H39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="34"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="34"/>
+      <x:c r="G41"/>
+      <x:c r="H41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="34"/>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="34"/>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="34"/>
+      <x:c r="G44"/>
+      <x:c r="H44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="34"/>
+      <x:c r="G45"/>
+      <x:c r="H45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="34"/>
+      <x:c r="G46"/>
+      <x:c r="H46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="34"/>
+      <x:c r="G47"/>
+      <x:c r="H47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="34"/>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="34"/>
+      <x:c r="G49"/>
+      <x:c r="H49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="34"/>
+      <x:c r="G50"/>
+      <x:c r="H50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="34"/>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="34"/>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="34"/>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="34"/>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="34"/>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="34"/>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="34"/>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="34"/>
+      <x:c r="G58"/>
+      <x:c r="H58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="34"/>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="34"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="34"/>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="34"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="34"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="34"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="34"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="34"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="34"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="34"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="34"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="34"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="34"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="34"/>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="34"/>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="34"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="34"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="34"/>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="34"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="34"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="34"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="34"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="34"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="34"/>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="34"/>
+      <x:c r="G83"/>
+      <x:c r="H83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="34"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="34"/>
+      <x:c r="G85"/>
+      <x:c r="H85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="34"/>
+      <x:c r="G86"/>
+      <x:c r="H86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="34"/>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="34"/>
+      <x:c r="G88"/>
+      <x:c r="H88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="34"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="34"/>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="34"/>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="34"/>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="34"/>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="34"/>
+      <x:c r="G94"/>
+      <x:c r="H94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="34"/>
+      <x:c r="G95"/>
+      <x:c r="H95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="34"/>
+      <x:c r="G96"/>
+      <x:c r="H96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="34"/>
+      <x:c r="G97"/>
+      <x:c r="H97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="34"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="34"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="34"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="34"/>
+      <x:c r="G101"/>
+      <x:c r="H101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="34"/>
+      <x:c r="G102"/>
+      <x:c r="H102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="34"/>
+      <x:c r="G103"/>
+      <x:c r="H103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="34"/>
+      <x:c r="G104"/>
+      <x:c r="H104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="34"/>
+      <x:c r="G105"/>
+      <x:c r="H105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="34"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="34"/>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="34"/>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="34"/>
+      <x:c r="G109"/>
+      <x:c r="H109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="34"/>
+      <x:c r="G110"/>
+      <x:c r="H110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="34"/>
+      <x:c r="G111"/>
+      <x:c r="H111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="34"/>
+      <x:c r="G112"/>
+      <x:c r="H112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="34"/>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="34"/>
+      <x:c r="G114"/>
+      <x:c r="H114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="34"/>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="34"/>
+      <x:c r="G116"/>
+      <x:c r="H116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="34"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="34"/>
+      <x:c r="G118"/>
+      <x:c r="H118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="34"/>
+      <x:c r="G119"/>
+      <x:c r="H119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="34"/>
+      <x:c r="G120"/>
+      <x:c r="H120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="34"/>
+      <x:c r="G121"/>
+      <x:c r="H121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="34"/>
+      <x:c r="G122"/>
+      <x:c r="H122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="34"/>
+      <x:c r="G123"/>
+      <x:c r="H123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="34"/>
+      <x:c r="G124"/>
+      <x:c r="H124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="34"/>
+      <x:c r="G125"/>
+      <x:c r="H125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="34"/>
+      <x:c r="G126"/>
+      <x:c r="H126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="34"/>
+      <x:c r="G127"/>
+      <x:c r="H127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="34"/>
+      <x:c r="G128"/>
+      <x:c r="H128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="34"/>
+      <x:c r="G129"/>
+      <x:c r="H129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="34"/>
+      <x:c r="G130"/>
+      <x:c r="H130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="34"/>
+      <x:c r="G131"/>
+      <x:c r="H131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="34"/>
+      <x:c r="G132"/>
+      <x:c r="H132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="34"/>
+      <x:c r="G133"/>
+      <x:c r="H133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="34"/>
+      <x:c r="G134"/>
+      <x:c r="H134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="34"/>
+      <x:c r="G135"/>
+      <x:c r="H135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="34"/>
+      <x:c r="G136"/>
+      <x:c r="H136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="34"/>
+      <x:c r="G137"/>
+      <x:c r="H137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="34"/>
+      <x:c r="G138"/>
+      <x:c r="H138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="34"/>
+      <x:c r="G139"/>
+      <x:c r="H139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="34"/>
+      <x:c r="G140"/>
+      <x:c r="H140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="34"/>
+      <x:c r="G141"/>
+      <x:c r="H141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="34"/>
+      <x:c r="G142"/>
+      <x:c r="H142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="34"/>
+      <x:c r="G143"/>
+      <x:c r="H143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="34"/>
+      <x:c r="G144"/>
+      <x:c r="H144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="34"/>
+      <x:c r="G145"/>
+      <x:c r="H145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="34"/>
+      <x:c r="G146"/>
+      <x:c r="H146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="34"/>
+      <x:c r="G147"/>
+      <x:c r="H147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="34"/>
+      <x:c r="G148"/>
+      <x:c r="H148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="34"/>
+      <x:c r="G149"/>
+      <x:c r="H149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="34"/>
+      <x:c r="G150"/>
+      <x:c r="H150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="34"/>
+      <x:c r="G151"/>
+      <x:c r="H151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="34"/>
+      <x:c r="G152"/>
+      <x:c r="H152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="34"/>
+      <x:c r="G153"/>
+      <x:c r="H153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="34"/>
+      <x:c r="G154"/>
+      <x:c r="H154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="34"/>
+      <x:c r="G155"/>
+      <x:c r="H155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="34"/>
+      <x:c r="G156"/>
+      <x:c r="H156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="34"/>
+      <x:c r="G157"/>
+      <x:c r="H157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="34"/>
+      <x:c r="G158"/>
+      <x:c r="H158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="34"/>
+      <x:c r="G159"/>
+      <x:c r="H159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="34"/>
+      <x:c r="G160"/>
+      <x:c r="H160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="34"/>
+      <x:c r="G161"/>
+      <x:c r="H161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="34"/>
+      <x:c r="G162"/>
+      <x:c r="H162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="34"/>
+      <x:c r="G163"/>
+      <x:c r="H163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="34"/>
+      <x:c r="G164"/>
+      <x:c r="H164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="34"/>
+      <x:c r="G165"/>
+      <x:c r="H165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="34"/>
+      <x:c r="G166"/>
+      <x:c r="H166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="34"/>
+      <x:c r="G167"/>
+      <x:c r="H167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="34"/>
+      <x:c r="G168"/>
+      <x:c r="H168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="34"/>
+      <x:c r="G169"/>
+      <x:c r="H169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="34"/>
+      <x:c r="G170"/>
+      <x:c r="H170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="34"/>
+      <x:c r="G171"/>
+      <x:c r="H171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="34"/>
+      <x:c r="G172"/>
+      <x:c r="H172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="34"/>
+      <x:c r="G173"/>
+      <x:c r="H173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="34"/>
+      <x:c r="G174"/>
+      <x:c r="H174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="34"/>
+      <x:c r="G175"/>
+      <x:c r="H175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="34"/>
+      <x:c r="G176"/>
+      <x:c r="H176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="34"/>
+      <x:c r="G177"/>
+      <x:c r="H177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="34"/>
+      <x:c r="G178"/>
+      <x:c r="H178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="34"/>
+      <x:c r="G179"/>
+      <x:c r="H179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="34"/>
+      <x:c r="G180"/>
+      <x:c r="H180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="34"/>
+      <x:c r="G181"/>
+      <x:c r="H181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="34"/>
+      <x:c r="G182"/>
+      <x:c r="H182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="34"/>
+      <x:c r="G183"/>
+      <x:c r="H183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="34"/>
+      <x:c r="G184"/>
+      <x:c r="H184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="34"/>
+      <x:c r="G185"/>
+      <x:c r="H185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="34"/>
+      <x:c r="G186"/>
+      <x:c r="H186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="34"/>
+      <x:c r="G187"/>
+      <x:c r="H187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="34"/>
+      <x:c r="G188"/>
+      <x:c r="H188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="34"/>
+      <x:c r="G189"/>
+      <x:c r="H189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="34"/>
+      <x:c r="G190"/>
+      <x:c r="H190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="34"/>
+      <x:c r="G191"/>
+      <x:c r="H191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="34"/>
+      <x:c r="G192"/>
+      <x:c r="H192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="34"/>
+      <x:c r="G193"/>
+      <x:c r="H193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="34"/>
+      <x:c r="G194"/>
+      <x:c r="H194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="34"/>
+      <x:c r="G195"/>
+      <x:c r="H195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="34"/>
+      <x:c r="G196"/>
+      <x:c r="H196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="34"/>
+      <x:c r="G197"/>
+      <x:c r="H197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="34"/>
+      <x:c r="G198"/>
+      <x:c r="H198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="34"/>
+      <x:c r="G199"/>
+      <x:c r="H199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="34"/>
+      <x:c r="G200"/>
+      <x:c r="H200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="34"/>
+      <x:c r="G201"/>
+      <x:c r="H201"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="34"/>
+      <x:c r="G202"/>
+      <x:c r="H202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="34"/>
+      <x:c r="G203"/>
+      <x:c r="H203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="34"/>
+      <x:c r="G204"/>
+      <x:c r="H204"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="34"/>
+      <x:c r="G205"/>
+      <x:c r="H205"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="34"/>
+      <x:c r="G206"/>
+      <x:c r="H206"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="34"/>
+      <x:c r="G207"/>
+      <x:c r="H207"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="34"/>
@@ -2107,10 +2503,10 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:dataValidations count="7">
+  <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="A5:A504">
       <x:formula1>"msycs,142yyq03,142yyq01,李四001"</x:formula1>
     </x:dataValidation>
@@ -2121,15 +2517,12 @@
       <x:formula1>"股票,期货,期权,互换"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F5:F504">
-      <x:formula1>"买,卖"</x:formula1>
+      <x:formula1>"买入,卖出,买开,卖开,买平,卖平"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G5:G504">
-      <x:formula1>"默认,开仓,平仓"</x:formula1>
+      <x:formula1>"默认模板,test1,test2,test3,test4,sjn-mock1,sjn-mock2"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H5:H504">
-      <x:formula1>"默认模板,test1,test2,test3,test4,sjn-mock1,sjn-mock2"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="I5:I504">
       <x:formula1>"新增,覆盖"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -2247,66 +2640,64 @@
         <x:v>是</x:v>
       </x:c>
       <x:c r="C9" s="46" t="str">
-        <x:v>独立字段，只能填写“买”或“卖”</x:v>
+        <x:v>只能填写“买入”“卖出”“买开”“卖开”“买平”或“卖平”</x:v>
       </x:c>
       <x:c r="D9" s="46" t="str">
-        <x:v>卖</x:v>
+        <x:v>卖开</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="31" customHeight="1">
       <x:c r="A10" s="46" t="str">
-        <x:v>开平标志</x:v>
+        <x:v>报单排序模板</x:v>
       </x:c>
       <x:c r="B10" s="46" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="C10" s="46" t="str">
-        <x:v>独立字段，只能填写“默认”“开仓”或“平仓”</x:v>
+        <x:v>必须是报单顺序配置中已有的模板名称</x:v>
       </x:c>
       <x:c r="D10" s="46" t="str">
-        <x:v>开仓</x:v>
+        <x:v>test1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="31" customHeight="1">
       <x:c r="A11" s="46" t="str">
-        <x:v>报单排序模板</x:v>
+        <x:v>导入方式</x:v>
       </x:c>
       <x:c r="B11" s="46" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="C11" s="46" t="str">
-        <x:v>必须是报单顺序配置中已有的模板名称</x:v>
+        <x:v>新增：追加规则；覆盖：替换该账户全部规则</x:v>
       </x:c>
       <x:c r="D11" s="46" t="str">
-        <x:v>test1</x:v>
+        <x:v>新增</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="31" customHeight="1">
-      <x:c r="A12" s="47" t="str">
-        <x:v>导入方式</x:v>
-      </x:c>
-      <x:c r="B12" s="47" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="C12" s="47" t="str">
-        <x:v>新增：追加规则；覆盖：替换该账户全部规则</x:v>
-      </x:c>
-      <x:c r="D12" s="47" t="str">
-        <x:v>新增</x:v>
-      </x:c>
+      <x:c r="A12" s="47"/>
+      <x:c r="B12" s="47"/>
+      <x:c r="C12" s="47"/>
+      <x:c r="D12" s="47"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>提示：同一交易账户在一次导入中只能使用一种导入方式。建议先使用“新增”验证，确认无误后再使用“覆盖”。</x:v>
+      </x:c>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
-      <x:c r="A14" s="51" t="str">
-        <x:v>提示：同一交易账户在一次导入中只能使用一种导入方式。建议先使用“新增”验证，确认无误后再使用“覆盖”。</x:v>
-      </x:c>
-      <x:c r="B14" s="51"/>
-      <x:c r="C14" s="51"/>
-      <x:c r="D14" s="51"/>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A14:D14"/>
+    <x:mergeCell ref="A13:D13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
